--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
     <t>Identifiant de l’entrée</t>
   </si>
   <si>
-    <t>fr-lm-traitement-dispense.code</t>
+    <t>fr-lm-traitement-dispense.completude</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -273,14 +273,10 @@
     <t>Complétude de la dispensation</t>
   </si>
   <si>
-    <t>fr-lm-traitement-dispense.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Texte de l'entrée</t>
+    <t>Valeur issue du JDV_CompletudeDispensation_CISIS (1.2.250.1.213.1.1.5.765)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis</t>
   </si>
   <si>
     <t>fr-lm-traitement-dispense.quantite</t>
@@ -313,44 +309,46 @@
     <t>Référence de la prescription</t>
   </si>
   <si>
-    <t>fr-lm-traitement-dispense.traitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement
+    <t>fr-lm-traitement-dispense.posologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-posologie
 </t>
   </si>
   <si>
     <t>Posologie</t>
   </si>
   <si>
-    <t>fr-lm-traitement-dispense.instructionsPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-instructions-patient
+    <t>fr-lm-traitement-dispense.notesDispensateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Instructions au patient</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-dispense.notesDispensateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-notes-dispensateur
+    <t>Notes du dispensateur</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-dispense.autorisationSubstitution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Notes du dispensateur</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-dispense.substitution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-acte-substitution
-</t>
-  </si>
-  <si>
-    <t>Substitution</t>
+    <t>Autorisation de substitution</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-dispense.autorisationSubstitution.type</t>
+  </si>
+  <si>
+    <t>Type de substitution jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis (2.16.840.1.113883.1.11.16621)</t>
+  </si>
+  <si>
+    <t>HL7_SubstanceAdminSubstitution</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis</t>
   </si>
 </sst>
 </file>
@@ -652,11 +650,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.53125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.53125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -679,14 +677,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.36328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.33984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.52734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="44.53125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1066,10 +1064,10 @@
         <v>73</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>73</v>
@@ -1104,10 +1102,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1130,13 +1128,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1187,7 +1185,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -1204,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1230,13 +1228,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1287,7 +1285,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
@@ -1304,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1315,7 +1313,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>79</v>
@@ -1330,13 +1328,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1387,10 +1385,10 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>79</v>
@@ -1404,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1430,13 +1428,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1487,7 +1485,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1504,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1530,13 +1528,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1587,7 +1585,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1604,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1615,7 +1613,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>79</v>
@@ -1630,13 +1628,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1687,10 +1685,10 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>79</v>
@@ -1704,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1730,13 +1728,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1766,10 +1764,10 @@
         <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -1787,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1799,106 +1797,6 @@
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
